--- a/data/trans_camb/LAWTONB_2R3-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R3-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,96; 14,94</t>
+          <t>3,74; 15,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 10,77</t>
+          <t>0,4; 11,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 18,3</t>
+          <t>7,68; 18,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 13,94</t>
+          <t>4,04; 13,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,98</t>
+          <t>3,12; 13,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 23,74</t>
+          <t>14,42; 23,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 12,72</t>
+          <t>5,42; 12,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 11,01</t>
+          <t>3,26; 10,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,28; 20,22</t>
+          <t>13,5; 20,4</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,71; 125,85</t>
+          <t>22,76; 133,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 88,02</t>
+          <t>1,76; 93,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,41; 155,04</t>
+          <t>44,49; 159,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,76; 81,13</t>
+          <t>18,39; 80,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 74,67</t>
+          <t>13,13; 75,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,97; 140,77</t>
+          <t>62,4; 138,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,75; 80,3</t>
+          <t>28,87; 83,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,73; 68,07</t>
+          <t>17,85; 68,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,61; 130,18</t>
+          <t>68,86; 133,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 13,49</t>
+          <t>-6,61; 12,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 2,5</t>
+          <t>-12,47; 2,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 5,87</t>
+          <t>-8,04; 6,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 9,46</t>
+          <t>-13,82; 9,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 12,52</t>
+          <t>-8,55; 12,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 3,88</t>
+          <t>-19,25; 4,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 8,26</t>
+          <t>-6,17; 8,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 5,84</t>
+          <t>-7,01; 5,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 2,74</t>
+          <t>-11,6; 2,78</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,95; 210,74</t>
+          <t>-43,06; 202,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-73,36; 44,54</t>
+          <t>-70,38; 58,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,68; 107,99</t>
+          <t>-46,4; 116,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,57; 183,12</t>
+          <t>-72,94; 162,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 238,0</t>
+          <t>-42,97; 221,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,2; 42,84</t>
+          <t>-83,74; 52,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,66; 99,14</t>
+          <t>-38,95; 124,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,97; 82,76</t>
+          <t>-43,21; 68,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,31; 28,35</t>
+          <t>-68,57; 31,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 15,59</t>
+          <t>-11,7; 16,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 14,99</t>
+          <t>-9,72; 15,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 6,34</t>
+          <t>-13,63; 6,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 25,84</t>
+          <t>-16,91; 23,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 16,43</t>
+          <t>-19,85; 14,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 8,83</t>
+          <t>-20,31; 9,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 15,81</t>
+          <t>-8,77; 15,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 11,65</t>
+          <t>-8,54; 12,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 5,01</t>
+          <t>-11,24; 5,24</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-86,42; —</t>
+          <t>-85,36; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,12; 293,94</t>
+          <t>-76,5; 280,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-69,3; 645,76</t>
+          <t>-76,4; 372,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-67,82; 347,96</t>
+          <t>-72,28; 436,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-68,35; 142,1</t>
+          <t>-66,52; 185,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,19; 12,95</t>
+          <t>3,45; 12,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 6,3</t>
+          <t>-1,84; 6,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 7,07</t>
+          <t>0,02; 7,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 11,57</t>
+          <t>3,02; 12,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 9,4</t>
+          <t>0,09; 9,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 11,38</t>
+          <t>-8,22; 10,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,77; 10,64</t>
+          <t>4,35; 10,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,85</t>
+          <t>0,96; 6,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 8,12</t>
+          <t>-3,58; 8,01</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,96; 117,76</t>
+          <t>22,5; 117,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 56,54</t>
+          <t>-12,84; 55,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 63,67</t>
+          <t>-0,27; 66,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,39; 72,73</t>
+          <t>14,15; 73,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 57,76</t>
+          <t>0,57; 56,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 65,19</t>
+          <t>-38,19; 61,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,82; 72,53</t>
+          <t>24,37; 74,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,35; 47,37</t>
+          <t>5,48; 48,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 53,23</t>
+          <t>-18,25; 51,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/LAWTONB_2R3-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R3-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,76</t>
+          <t>11,98</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,86</t>
+          <t>18,91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16,96</t>
+          <t>16,72</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,74; 15,15</t>
+          <t>4,13; 14,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 11,01</t>
+          <t>0,89; 11,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 18,76</t>
+          <t>6,68; 17,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 13,9</t>
+          <t>3,6; 13,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 13,55</t>
+          <t>3,15; 13,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,42; 23,57</t>
+          <t>14,05; 23,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 12,75</t>
+          <t>4,97; 12,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 10,78</t>
+          <t>3,48; 11,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,5; 20,4</t>
+          <t>13,08; 20,33</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,76; 133,16</t>
+          <t>25,97; 135,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 93,52</t>
+          <t>5,26; 100,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,49; 159,52</t>
+          <t>37,63; 147,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,39; 80,48</t>
+          <t>16,16; 78,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,13; 75,26</t>
+          <t>12,97; 78,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,4; 138,44</t>
+          <t>63,42; 140,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,87; 83,91</t>
+          <t>25,86; 79,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 68,63</t>
+          <t>18,4; 71,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,86; 133,05</t>
+          <t>67,78; 131,98</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,91</t>
+          <t>2,0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 12,79</t>
+          <t>-5,58; 13,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 2,88</t>
+          <t>-11,63; 3,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 6,29</t>
+          <t>-10,11; 5,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 9,29</t>
+          <t>-13,14; 9,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 12,5</t>
+          <t>-9,9; 11,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 4,45</t>
+          <t>-9,16; 10,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 8,85</t>
+          <t>-6,25; 8,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 5,34</t>
+          <t>-7,94; 5,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 2,78</t>
+          <t>-6,38; 5,52</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-4,29%</t>
+          <t>-7,31%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-39,1%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-25,05%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-43,06; 202,79</t>
+          <t>-39,75; 209,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,38; 58,27</t>
+          <t>-70,24; 56,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,4; 116,18</t>
+          <t>-51,74; 98,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,94; 162,95</t>
+          <t>-65,17; 159,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,97; 221,65</t>
+          <t>-50,1; 196,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,74; 52,21</t>
+          <t>-41,78; 182,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,95; 124,28</t>
+          <t>-40,49; 122,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,21; 68,65</t>
+          <t>-45,93; 71,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-68,57; 31,13</t>
+          <t>-36,33; 75,03</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,54</t>
+          <t>-2,52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-0,86</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 16,73</t>
+          <t>-11,14; 16,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 15,83</t>
+          <t>-10,73; 15,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 6,87</t>
+          <t>-13,06; 7,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 23,29</t>
+          <t>-14,98; 25,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 14,36</t>
+          <t>-19,1; 14,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 9,21</t>
+          <t>-20,81; 8,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 15,01</t>
+          <t>-9,34; 14,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 12,23</t>
+          <t>-8,92; 11,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 5,24</t>
+          <t>-11,18; 5,7</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-5,95%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-20,67%</t>
+          <t>-20,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-13,57%</t>
+          <t>-9,86%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,36; —</t>
+          <t>-82,26; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-76,5; 280,62</t>
+          <t>-75,64; 239,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,4; 372,36</t>
+          <t>-76,92; 398,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,28; 436,4</t>
+          <t>-65,77; 372,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,52; 185,43</t>
+          <t>-65,8; 181,94</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>9,82</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>6,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 12,68</t>
+          <t>3,25; 12,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,04</t>
+          <t>-1,64; 6,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 7,16</t>
+          <t>-0,62; 6,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 12,07</t>
+          <t>2,68; 11,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 9,2</t>
+          <t>0,78; 9,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 10,82</t>
+          <t>6,0; 13,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 10,62</t>
+          <t>4,22; 11,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 6,97</t>
+          <t>0,38; 6,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 8,01</t>
+          <t>4,01; 9,53</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>41,92%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,5; 117,73</t>
+          <t>20,35; 112,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 55,27</t>
+          <t>-12,0; 55,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 66,71</t>
+          <t>-4,06; 62,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,15; 73,22</t>
+          <t>12,58; 71,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 56,52</t>
+          <t>3,71; 58,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,19; 61,01</t>
+          <t>27,75; 86,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,37; 74,21</t>
+          <t>23,76; 75,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,48; 48,05</t>
+          <t>2,36; 46,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 51,87</t>
+          <t>22,17; 67,67</t>
         </is>
       </c>
     </row>
